--- a/evaluation_forms/032_logo_presentation_evaluation_form_template--evaluation_forms.xlsx
+++ b/evaluation_forms/032_logo_presentation_evaluation_form_template--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Logo Presentation Evaluation Form</t>
+          <t>Overall Presentation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>Color Scheme Effectiveness</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Form Subcategory</t>
+          <t>Composition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form Comment</t>
+          <t>Typography Effectiveness</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form Rating</t>
+          <t>Overall Impression</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form Comment</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +686,105 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Form Subcategory</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>form_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>form_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>form_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Logo Type</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>form_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Logo Size</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -740,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>logo_concept</t>
+          <t>logo_design</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logo Concept</t>
+          <t>Logo Design</t>
         </is>
       </c>
     </row>
@@ -803,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -820,51 +912,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>color_scheme</t>
+          <t>brand_guidelines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Color Scheme</t>
+          <t>Brand Guidelines</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>typography</t>
+          <t>design_style</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Design Style</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>logo_design</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Composition</t>
+          <t>Logo Design</t>
         </is>
       </c>
     </row>
@@ -876,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>logo_design</t>
+          <t>color_scheme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Logo Design</t>
+          <t>Color Scheme</t>
         </is>
       </c>
     </row>
@@ -893,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>brand_guidelines</t>
+          <t>typography</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brand Guidelines</t>
+          <t>Typography</t>
         </is>
       </c>
     </row>
@@ -910,97 +1002,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>design_style</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design Style</t>
+          <t>Composition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_7_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>overall_impression</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overall Impression</t>
+          <t>Icon</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>logo_design</t>
+          <t>wordmark</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Logo Design</t>
+          <t>Wordmark</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>color_scheme</t>
+          <t>lettermark</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Color Scheme</t>
+          <t>Lettermark</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>form_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>typography</t>
+          <t>emblem</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Typography</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>form_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>composition</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Composition</t>
+          <t>Emblem</t>
         </is>
       </c>
     </row>
